--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.79862945178746</v>
+        <v>10.04227728591546</v>
       </c>
       <c r="D2" t="n">
-        <v>60.68275465820567</v>
+        <v>9.860947631958421</v>
       </c>
       <c r="E2" t="n">
-        <v>11.94604343169033</v>
+        <v>1.94123205764968</v>
       </c>
       <c r="F2" t="n">
-        <v>11.24038829348907</v>
+        <v>1.826563097691973</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.49396628913598</v>
+        <v>5.442769521984597</v>
       </c>
       <c r="D3" t="n">
-        <v>33.9374133976164</v>
+        <v>5.514829677112666</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94604343169033</v>
+        <v>1.94123205764968</v>
       </c>
       <c r="F3" t="n">
-        <v>11.24038829348907</v>
+        <v>1.826563097691973</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.21820919964568</v>
+        <v>6.697958994942424</v>
       </c>
       <c r="D4" t="n">
-        <v>41.64673509915933</v>
+        <v>6.767594453613391</v>
       </c>
       <c r="E4" t="n">
-        <v>11.94604343169033</v>
+        <v>1.94123205764968</v>
       </c>
       <c r="F4" t="n">
-        <v>11.24038829348907</v>
+        <v>1.826563097691973</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
